--- a/scripts/python/sf-doc-mcp/画面設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/画面設計書テンプレート.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,7 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font/>
   </fonts>
   <fills count="6">
     <fill>
@@ -87,7 +88,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -295,11 +296,12 @@
         <color rgb="001F3864"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -330,6 +332,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1487,10 +1493,10 @@
   </sheetData>
   <mergeCells count="173">
     <mergeCell ref="D20:E20"/>
+    <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="R24:W24"/>
     <mergeCell ref="AA5:AC5"/>
-    <mergeCell ref="AD17:AE17"/>
     <mergeCell ref="L15:Q15"/>
-    <mergeCell ref="R24:W24"/>
     <mergeCell ref="X18:Z18"/>
     <mergeCell ref="L18:Q18"/>
     <mergeCell ref="B3:F3"/>
@@ -1528,8 +1534,8 @@
     <mergeCell ref="X7:Z7"/>
     <mergeCell ref="L12:Q12"/>
     <mergeCell ref="F15:K15"/>
+    <mergeCell ref="AD18:AE18"/>
     <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AD18:AE18"/>
     <mergeCell ref="F24:K24"/>
     <mergeCell ref="R6:W6"/>
     <mergeCell ref="B16:C16"/>
@@ -1670,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AE41"/>
+  <dimension ref="A1:AE41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2007,588 +2013,632 @@
       <c r="AE19" s="10" t="n"/>
     </row>
     <row r="20" ht="12" customHeight="1"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>6. 画面イメージ（ワイヤーフレーム / キャプチャ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
-      <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="12" t="n"/>
-      <c r="R22" s="12" t="n"/>
-      <c r="S22" s="12" t="n"/>
-      <c r="T22" s="12" t="n"/>
-      <c r="U22" s="12" t="n"/>
-      <c r="V22" s="12" t="n"/>
-      <c r="W22" s="12" t="n"/>
-      <c r="X22" s="12" t="n"/>
-      <c r="Y22" s="12" t="n"/>
-      <c r="Z22" s="12" t="n"/>
-      <c r="AA22" s="12" t="n"/>
-      <c r="AB22" s="12" t="n"/>
-      <c r="AC22" s="12" t="n"/>
-      <c r="AD22" s="12" t="n"/>
-      <c r="AE22" s="13" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="14" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-      <c r="H23" s="14" t="n"/>
-      <c r="I23" s="14" t="n"/>
-      <c r="J23" s="14" t="n"/>
-      <c r="K23" s="14" t="n"/>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="14" t="n"/>
-      <c r="N23" s="14" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
-      <c r="Q23" s="14" t="n"/>
-      <c r="R23" s="14" t="n"/>
-      <c r="S23" s="14" t="n"/>
-      <c r="T23" s="14" t="n"/>
-      <c r="U23" s="14" t="n"/>
-      <c r="V23" s="14" t="n"/>
-      <c r="W23" s="14" t="n"/>
-      <c r="X23" s="14" t="n"/>
-      <c r="Y23" s="14" t="n"/>
-      <c r="Z23" s="14" t="n"/>
-      <c r="AA23" s="14" t="n"/>
-      <c r="AB23" s="14" t="n"/>
-      <c r="AC23" s="14" t="n"/>
-      <c r="AD23" s="14" t="n"/>
-      <c r="AE23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="14" t="n"/>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="14" t="n"/>
-      <c r="N24" s="14" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14" t="n"/>
-      <c r="Q24" s="14" t="n"/>
-      <c r="R24" s="14" t="n"/>
-      <c r="S24" s="14" t="n"/>
-      <c r="T24" s="14" t="n"/>
-      <c r="U24" s="14" t="n"/>
-      <c r="V24" s="14" t="n"/>
-      <c r="W24" s="14" t="n"/>
-      <c r="X24" s="14" t="n"/>
-      <c r="Y24" s="14" t="n"/>
-      <c r="Z24" s="14" t="n"/>
-      <c r="AA24" s="14" t="n"/>
-      <c r="AB24" s="14" t="n"/>
-      <c r="AC24" s="14" t="n"/>
-      <c r="AD24" s="14" t="n"/>
-      <c r="AE24" s="14" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
-      <c r="K25" s="14" t="n"/>
-      <c r="L25" s="14" t="n"/>
-      <c r="M25" s="14" t="n"/>
-      <c r="N25" s="14" t="n"/>
-      <c r="O25" s="14" t="n"/>
-      <c r="P25" s="14" t="n"/>
-      <c r="Q25" s="14" t="n"/>
-      <c r="R25" s="14" t="n"/>
-      <c r="S25" s="14" t="n"/>
-      <c r="T25" s="14" t="n"/>
-      <c r="U25" s="14" t="n"/>
-      <c r="V25" s="14" t="n"/>
-      <c r="W25" s="14" t="n"/>
-      <c r="X25" s="14" t="n"/>
-      <c r="Y25" s="14" t="n"/>
-      <c r="Z25" s="14" t="n"/>
-      <c r="AA25" s="14" t="n"/>
-      <c r="AB25" s="14" t="n"/>
-      <c r="AC25" s="14" t="n"/>
-      <c r="AD25" s="14" t="n"/>
-      <c r="AE25" s="14" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="n"/>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="14" t="n"/>
-      <c r="L26" s="14" t="n"/>
-      <c r="M26" s="14" t="n"/>
-      <c r="N26" s="14" t="n"/>
-      <c r="O26" s="14" t="n"/>
-      <c r="P26" s="14" t="n"/>
-      <c r="Q26" s="14" t="n"/>
-      <c r="R26" s="14" t="n"/>
-      <c r="S26" s="14" t="n"/>
-      <c r="T26" s="14" t="n"/>
-      <c r="U26" s="14" t="n"/>
-      <c r="V26" s="14" t="n"/>
-      <c r="W26" s="14" t="n"/>
-      <c r="X26" s="14" t="n"/>
-      <c r="Y26" s="14" t="n"/>
-      <c r="Z26" s="14" t="n"/>
-      <c r="AA26" s="14" t="n"/>
-      <c r="AB26" s="14" t="n"/>
-      <c r="AC26" s="14" t="n"/>
-      <c r="AD26" s="14" t="n"/>
-      <c r="AE26" s="14" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="14" t="n"/>
-      <c r="I27" s="14" t="n"/>
-      <c r="J27" s="14" t="n"/>
-      <c r="K27" s="14" t="n"/>
-      <c r="L27" s="14" t="n"/>
-      <c r="M27" s="14" t="n"/>
-      <c r="N27" s="14" t="n"/>
-      <c r="O27" s="14" t="n"/>
-      <c r="P27" s="14" t="n"/>
-      <c r="Q27" s="14" t="n"/>
-      <c r="R27" s="14" t="n"/>
-      <c r="S27" s="14" t="n"/>
-      <c r="T27" s="14" t="n"/>
-      <c r="U27" s="14" t="n"/>
-      <c r="V27" s="14" t="n"/>
-      <c r="W27" s="14" t="n"/>
-      <c r="X27" s="14" t="n"/>
-      <c r="Y27" s="14" t="n"/>
-      <c r="Z27" s="14" t="n"/>
-      <c r="AA27" s="14" t="n"/>
-      <c r="AB27" s="14" t="n"/>
-      <c r="AC27" s="14" t="n"/>
-      <c r="AD27" s="14" t="n"/>
-      <c r="AE27" s="14" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="14" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="14" t="n"/>
-      <c r="I28" s="14" t="n"/>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="14" t="n"/>
-      <c r="L28" s="14" t="n"/>
-      <c r="M28" s="14" t="n"/>
-      <c r="N28" s="14" t="n"/>
-      <c r="O28" s="14" t="n"/>
-      <c r="P28" s="14" t="n"/>
-      <c r="Q28" s="14" t="n"/>
-      <c r="R28" s="14" t="n"/>
-      <c r="S28" s="14" t="n"/>
-      <c r="T28" s="14" t="n"/>
-      <c r="U28" s="14" t="n"/>
-      <c r="V28" s="14" t="n"/>
-      <c r="W28" s="14" t="n"/>
-      <c r="X28" s="14" t="n"/>
-      <c r="Y28" s="14" t="n"/>
-      <c r="Z28" s="14" t="n"/>
-      <c r="AA28" s="14" t="n"/>
-      <c r="AB28" s="14" t="n"/>
-      <c r="AC28" s="14" t="n"/>
-      <c r="AD28" s="14" t="n"/>
-      <c r="AE28" s="14" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-      <c r="I29" s="14" t="n"/>
-      <c r="J29" s="14" t="n"/>
-      <c r="K29" s="14" t="n"/>
-      <c r="L29" s="14" t="n"/>
-      <c r="M29" s="14" t="n"/>
-      <c r="N29" s="14" t="n"/>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="14" t="n"/>
-      <c r="Q29" s="14" t="n"/>
-      <c r="R29" s="14" t="n"/>
-      <c r="S29" s="14" t="n"/>
-      <c r="T29" s="14" t="n"/>
-      <c r="U29" s="14" t="n"/>
-      <c r="V29" s="14" t="n"/>
-      <c r="W29" s="14" t="n"/>
-      <c r="X29" s="14" t="n"/>
-      <c r="Y29" s="14" t="n"/>
-      <c r="Z29" s="14" t="n"/>
-      <c r="AA29" s="14" t="n"/>
-      <c r="AB29" s="14" t="n"/>
-      <c r="AC29" s="14" t="n"/>
-      <c r="AD29" s="14" t="n"/>
-      <c r="AE29" s="14" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="14" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="14" t="n"/>
-      <c r="M30" s="14" t="n"/>
-      <c r="N30" s="14" t="n"/>
-      <c r="O30" s="14" t="n"/>
-      <c r="P30" s="14" t="n"/>
-      <c r="Q30" s="14" t="n"/>
-      <c r="R30" s="14" t="n"/>
-      <c r="S30" s="14" t="n"/>
-      <c r="T30" s="14" t="n"/>
-      <c r="U30" s="14" t="n"/>
-      <c r="V30" s="14" t="n"/>
-      <c r="W30" s="14" t="n"/>
-      <c r="X30" s="14" t="n"/>
-      <c r="Y30" s="14" t="n"/>
-      <c r="Z30" s="14" t="n"/>
-      <c r="AA30" s="14" t="n"/>
-      <c r="AB30" s="14" t="n"/>
-      <c r="AC30" s="14" t="n"/>
-      <c r="AD30" s="14" t="n"/>
-      <c r="AE30" s="14" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="14" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="14" t="n"/>
-      <c r="L31" s="14" t="n"/>
-      <c r="M31" s="14" t="n"/>
-      <c r="N31" s="14" t="n"/>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="14" t="n"/>
-      <c r="Q31" s="14" t="n"/>
-      <c r="R31" s="14" t="n"/>
-      <c r="S31" s="14" t="n"/>
-      <c r="T31" s="14" t="n"/>
-      <c r="U31" s="14" t="n"/>
-      <c r="V31" s="14" t="n"/>
-      <c r="W31" s="14" t="n"/>
-      <c r="X31" s="14" t="n"/>
-      <c r="Y31" s="14" t="n"/>
-      <c r="Z31" s="14" t="n"/>
-      <c r="AA31" s="14" t="n"/>
-      <c r="AB31" s="14" t="n"/>
-      <c r="AC31" s="14" t="n"/>
-      <c r="AD31" s="14" t="n"/>
-      <c r="AE31" s="14" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="14" t="n"/>
-      <c r="L32" s="14" t="n"/>
-      <c r="M32" s="14" t="n"/>
-      <c r="N32" s="14" t="n"/>
-      <c r="O32" s="14" t="n"/>
-      <c r="P32" s="14" t="n"/>
-      <c r="Q32" s="14" t="n"/>
-      <c r="R32" s="14" t="n"/>
-      <c r="S32" s="14" t="n"/>
-      <c r="T32" s="14" t="n"/>
-      <c r="U32" s="14" t="n"/>
-      <c r="V32" s="14" t="n"/>
-      <c r="W32" s="14" t="n"/>
-      <c r="X32" s="14" t="n"/>
-      <c r="Y32" s="14" t="n"/>
-      <c r="Z32" s="14" t="n"/>
-      <c r="AA32" s="14" t="n"/>
-      <c r="AB32" s="14" t="n"/>
-      <c r="AC32" s="14" t="n"/>
-      <c r="AD32" s="14" t="n"/>
-      <c r="AE32" s="14" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="14" t="n"/>
-      <c r="L33" s="14" t="n"/>
-      <c r="M33" s="14" t="n"/>
-      <c r="N33" s="14" t="n"/>
-      <c r="O33" s="14" t="n"/>
-      <c r="P33" s="14" t="n"/>
-      <c r="Q33" s="14" t="n"/>
-      <c r="R33" s="14" t="n"/>
-      <c r="S33" s="14" t="n"/>
-      <c r="T33" s="14" t="n"/>
-      <c r="U33" s="14" t="n"/>
-      <c r="V33" s="14" t="n"/>
-      <c r="W33" s="14" t="n"/>
-      <c r="X33" s="14" t="n"/>
-      <c r="Y33" s="14" t="n"/>
-      <c r="Z33" s="14" t="n"/>
-      <c r="AA33" s="14" t="n"/>
-      <c r="AB33" s="14" t="n"/>
-      <c r="AC33" s="14" t="n"/>
-      <c r="AD33" s="14" t="n"/>
-      <c r="AE33" s="14" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="14" t="n"/>
-      <c r="K34" s="14" t="n"/>
-      <c r="L34" s="14" t="n"/>
-      <c r="M34" s="14" t="n"/>
-      <c r="N34" s="14" t="n"/>
-      <c r="O34" s="14" t="n"/>
-      <c r="P34" s="14" t="n"/>
-      <c r="Q34" s="14" t="n"/>
-      <c r="R34" s="14" t="n"/>
-      <c r="S34" s="14" t="n"/>
-      <c r="T34" s="14" t="n"/>
-      <c r="U34" s="14" t="n"/>
-      <c r="V34" s="14" t="n"/>
-      <c r="W34" s="14" t="n"/>
-      <c r="X34" s="14" t="n"/>
-      <c r="Y34" s="14" t="n"/>
-      <c r="Z34" s="14" t="n"/>
-      <c r="AA34" s="14" t="n"/>
-      <c r="AB34" s="14" t="n"/>
-      <c r="AC34" s="14" t="n"/>
-      <c r="AD34" s="14" t="n"/>
-      <c r="AE34" s="14" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="14" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="14" t="n"/>
-      <c r="H35" s="14" t="n"/>
-      <c r="I35" s="14" t="n"/>
-      <c r="J35" s="14" t="n"/>
-      <c r="K35" s="14" t="n"/>
-      <c r="L35" s="14" t="n"/>
-      <c r="M35" s="14" t="n"/>
-      <c r="N35" s="14" t="n"/>
-      <c r="O35" s="14" t="n"/>
-      <c r="P35" s="14" t="n"/>
-      <c r="Q35" s="14" t="n"/>
-      <c r="R35" s="14" t="n"/>
-      <c r="S35" s="14" t="n"/>
-      <c r="T35" s="14" t="n"/>
-      <c r="U35" s="14" t="n"/>
-      <c r="V35" s="14" t="n"/>
-      <c r="W35" s="14" t="n"/>
-      <c r="X35" s="14" t="n"/>
-      <c r="Y35" s="14" t="n"/>
-      <c r="Z35" s="14" t="n"/>
-      <c r="AA35" s="14" t="n"/>
-      <c r="AB35" s="14" t="n"/>
-      <c r="AC35" s="14" t="n"/>
-      <c r="AD35" s="14" t="n"/>
-      <c r="AE35" s="14" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="14" t="n"/>
-      <c r="I36" s="14" t="n"/>
-      <c r="J36" s="14" t="n"/>
-      <c r="K36" s="14" t="n"/>
-      <c r="L36" s="14" t="n"/>
-      <c r="M36" s="14" t="n"/>
-      <c r="N36" s="14" t="n"/>
-      <c r="O36" s="14" t="n"/>
-      <c r="P36" s="14" t="n"/>
-      <c r="Q36" s="14" t="n"/>
-      <c r="R36" s="14" t="n"/>
-      <c r="S36" s="14" t="n"/>
-      <c r="T36" s="14" t="n"/>
-      <c r="U36" s="14" t="n"/>
-      <c r="V36" s="14" t="n"/>
-      <c r="W36" s="14" t="n"/>
-      <c r="X36" s="14" t="n"/>
-      <c r="Y36" s="14" t="n"/>
-      <c r="Z36" s="14" t="n"/>
-      <c r="AA36" s="14" t="n"/>
-      <c r="AB36" s="14" t="n"/>
-      <c r="AC36" s="14" t="n"/>
-      <c r="AD36" s="14" t="n"/>
-      <c r="AE36" s="14" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="14" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="14" t="n"/>
-      <c r="H37" s="14" t="n"/>
-      <c r="I37" s="14" t="n"/>
-      <c r="J37" s="14" t="n"/>
-      <c r="K37" s="14" t="n"/>
-      <c r="L37" s="14" t="n"/>
-      <c r="M37" s="14" t="n"/>
-      <c r="N37" s="14" t="n"/>
-      <c r="O37" s="14" t="n"/>
-      <c r="P37" s="14" t="n"/>
-      <c r="Q37" s="14" t="n"/>
-      <c r="R37" s="14" t="n"/>
-      <c r="S37" s="14" t="n"/>
-      <c r="T37" s="14" t="n"/>
-      <c r="U37" s="14" t="n"/>
-      <c r="V37" s="14" t="n"/>
-      <c r="W37" s="14" t="n"/>
-      <c r="X37" s="14" t="n"/>
-      <c r="Y37" s="14" t="n"/>
-      <c r="Z37" s="14" t="n"/>
-      <c r="AA37" s="14" t="n"/>
-      <c r="AB37" s="14" t="n"/>
-      <c r="AC37" s="14" t="n"/>
-      <c r="AD37" s="14" t="n"/>
-      <c r="AE37" s="14" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="14" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="14" t="n"/>
-      <c r="H38" s="14" t="n"/>
-      <c r="I38" s="14" t="n"/>
-      <c r="J38" s="14" t="n"/>
-      <c r="K38" s="14" t="n"/>
-      <c r="L38" s="14" t="n"/>
-      <c r="M38" s="14" t="n"/>
-      <c r="N38" s="14" t="n"/>
-      <c r="O38" s="14" t="n"/>
-      <c r="P38" s="14" t="n"/>
-      <c r="Q38" s="14" t="n"/>
-      <c r="R38" s="14" t="n"/>
-      <c r="S38" s="14" t="n"/>
-      <c r="T38" s="14" t="n"/>
-      <c r="U38" s="14" t="n"/>
-      <c r="V38" s="14" t="n"/>
-      <c r="W38" s="14" t="n"/>
-      <c r="X38" s="14" t="n"/>
-      <c r="Y38" s="14" t="n"/>
-      <c r="Z38" s="14" t="n"/>
-      <c r="AA38" s="14" t="n"/>
-      <c r="AB38" s="14" t="n"/>
-      <c r="AC38" s="14" t="n"/>
-      <c r="AD38" s="14" t="n"/>
-      <c r="AE38" s="14" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="14" t="n"/>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="14" t="n"/>
-      <c r="G39" s="14" t="n"/>
-      <c r="H39" s="14" t="n"/>
-      <c r="I39" s="14" t="n"/>
-      <c r="J39" s="14" t="n"/>
-      <c r="K39" s="14" t="n"/>
-      <c r="L39" s="14" t="n"/>
-      <c r="M39" s="14" t="n"/>
-      <c r="N39" s="14" t="n"/>
-      <c r="O39" s="14" t="n"/>
-      <c r="P39" s="14" t="n"/>
-      <c r="Q39" s="14" t="n"/>
-      <c r="R39" s="14" t="n"/>
-      <c r="S39" s="14" t="n"/>
-      <c r="T39" s="14" t="n"/>
-      <c r="U39" s="14" t="n"/>
-      <c r="V39" s="14" t="n"/>
-      <c r="W39" s="14" t="n"/>
-      <c r="X39" s="14" t="n"/>
-      <c r="Y39" s="14" t="n"/>
-      <c r="Z39" s="14" t="n"/>
-      <c r="AA39" s="14" t="n"/>
-      <c r="AB39" s="14" t="n"/>
-      <c r="AC39" s="14" t="n"/>
-      <c r="AD39" s="14" t="n"/>
-      <c r="AE39" s="14" t="n"/>
+    <row r="21" hidden="1">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="18" t="n"/>
+      <c r="P21" s="18" t="n"/>
+      <c r="Q21" s="18" t="n"/>
+      <c r="R21" s="18" t="n"/>
+      <c r="S21" s="18" t="n"/>
+      <c r="T21" s="18" t="n"/>
+      <c r="U21" s="18" t="n"/>
+      <c r="V21" s="18" t="n"/>
+      <c r="W21" s="18" t="n"/>
+      <c r="X21" s="18" t="n"/>
+      <c r="Y21" s="18" t="n"/>
+      <c r="Z21" s="18" t="n"/>
+      <c r="AA21" s="18" t="n"/>
+      <c r="AB21" s="18" t="n"/>
+      <c r="AC21" s="18" t="n"/>
+      <c r="AD21" s="18" t="n"/>
+      <c r="AE21" s="18" t="n"/>
+    </row>
+    <row r="22" hidden="1">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="18" t="n"/>
+      <c r="P22" s="18" t="n"/>
+      <c r="Q22" s="18" t="n"/>
+      <c r="R22" s="18" t="n"/>
+      <c r="S22" s="18" t="n"/>
+      <c r="T22" s="18" t="n"/>
+      <c r="U22" s="18" t="n"/>
+      <c r="V22" s="18" t="n"/>
+      <c r="W22" s="18" t="n"/>
+      <c r="X22" s="18" t="n"/>
+      <c r="Y22" s="18" t="n"/>
+      <c r="Z22" s="18" t="n"/>
+      <c r="AA22" s="18" t="n"/>
+      <c r="AB22" s="18" t="n"/>
+      <c r="AC22" s="18" t="n"/>
+      <c r="AD22" s="18" t="n"/>
+      <c r="AE22" s="18" t="n"/>
+    </row>
+    <row r="23" hidden="1">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="18" t="n"/>
+      <c r="P23" s="18" t="n"/>
+      <c r="Q23" s="18" t="n"/>
+      <c r="R23" s="18" t="n"/>
+      <c r="S23" s="18" t="n"/>
+      <c r="T23" s="18" t="n"/>
+      <c r="U23" s="18" t="n"/>
+      <c r="V23" s="18" t="n"/>
+      <c r="W23" s="18" t="n"/>
+      <c r="X23" s="18" t="n"/>
+      <c r="Y23" s="18" t="n"/>
+      <c r="Z23" s="18" t="n"/>
+      <c r="AA23" s="18" t="n"/>
+      <c r="AB23" s="18" t="n"/>
+      <c r="AC23" s="18" t="n"/>
+      <c r="AD23" s="18" t="n"/>
+      <c r="AE23" s="18" t="n"/>
+    </row>
+    <row r="24" hidden="1">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
+      <c r="P24" s="18" t="n"/>
+      <c r="Q24" s="18" t="n"/>
+      <c r="R24" s="18" t="n"/>
+      <c r="S24" s="18" t="n"/>
+      <c r="T24" s="18" t="n"/>
+      <c r="U24" s="18" t="n"/>
+      <c r="V24" s="18" t="n"/>
+      <c r="W24" s="18" t="n"/>
+      <c r="X24" s="18" t="n"/>
+      <c r="Y24" s="18" t="n"/>
+      <c r="Z24" s="18" t="n"/>
+      <c r="AA24" s="18" t="n"/>
+      <c r="AB24" s="18" t="n"/>
+      <c r="AC24" s="18" t="n"/>
+      <c r="AD24" s="18" t="n"/>
+      <c r="AE24" s="18" t="n"/>
+    </row>
+    <row r="25" hidden="1">
+      <c r="A25" s="18" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="18" t="n"/>
+      <c r="P25" s="18" t="n"/>
+      <c r="Q25" s="18" t="n"/>
+      <c r="R25" s="18" t="n"/>
+      <c r="S25" s="18" t="n"/>
+      <c r="T25" s="18" t="n"/>
+      <c r="U25" s="18" t="n"/>
+      <c r="V25" s="18" t="n"/>
+      <c r="W25" s="18" t="n"/>
+      <c r="X25" s="18" t="n"/>
+      <c r="Y25" s="18" t="n"/>
+      <c r="Z25" s="18" t="n"/>
+      <c r="AA25" s="18" t="n"/>
+      <c r="AB25" s="18" t="n"/>
+      <c r="AC25" s="18" t="n"/>
+      <c r="AD25" s="18" t="n"/>
+      <c r="AE25" s="18" t="n"/>
+    </row>
+    <row r="26" hidden="1">
+      <c r="A26" s="18" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="18" t="n"/>
+      <c r="P26" s="18" t="n"/>
+      <c r="Q26" s="18" t="n"/>
+      <c r="R26" s="18" t="n"/>
+      <c r="S26" s="18" t="n"/>
+      <c r="T26" s="18" t="n"/>
+      <c r="U26" s="18" t="n"/>
+      <c r="V26" s="18" t="n"/>
+      <c r="W26" s="18" t="n"/>
+      <c r="X26" s="18" t="n"/>
+      <c r="Y26" s="18" t="n"/>
+      <c r="Z26" s="18" t="n"/>
+      <c r="AA26" s="18" t="n"/>
+      <c r="AB26" s="18" t="n"/>
+      <c r="AC26" s="18" t="n"/>
+      <c r="AD26" s="18" t="n"/>
+      <c r="AE26" s="18" t="n"/>
+    </row>
+    <row r="27" hidden="1">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="18" t="n"/>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="18" t="n"/>
+      <c r="R27" s="18" t="n"/>
+      <c r="S27" s="18" t="n"/>
+      <c r="T27" s="18" t="n"/>
+      <c r="U27" s="18" t="n"/>
+      <c r="V27" s="18" t="n"/>
+      <c r="W27" s="18" t="n"/>
+      <c r="X27" s="18" t="n"/>
+      <c r="Y27" s="18" t="n"/>
+      <c r="Z27" s="18" t="n"/>
+      <c r="AA27" s="18" t="n"/>
+      <c r="AB27" s="18" t="n"/>
+      <c r="AC27" s="18" t="n"/>
+      <c r="AD27" s="18" t="n"/>
+      <c r="AE27" s="18" t="n"/>
+    </row>
+    <row r="28" hidden="1">
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
+      <c r="P28" s="18" t="n"/>
+      <c r="Q28" s="18" t="n"/>
+      <c r="R28" s="18" t="n"/>
+      <c r="S28" s="18" t="n"/>
+      <c r="T28" s="18" t="n"/>
+      <c r="U28" s="18" t="n"/>
+      <c r="V28" s="18" t="n"/>
+      <c r="W28" s="18" t="n"/>
+      <c r="X28" s="18" t="n"/>
+      <c r="Y28" s="18" t="n"/>
+      <c r="Z28" s="18" t="n"/>
+      <c r="AA28" s="18" t="n"/>
+      <c r="AB28" s="18" t="n"/>
+      <c r="AC28" s="18" t="n"/>
+      <c r="AD28" s="18" t="n"/>
+      <c r="AE28" s="18" t="n"/>
+    </row>
+    <row r="29" hidden="1">
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="18" t="n"/>
+      <c r="M29" s="18" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="18" t="n"/>
+      <c r="P29" s="18" t="n"/>
+      <c r="Q29" s="18" t="n"/>
+      <c r="R29" s="18" t="n"/>
+      <c r="S29" s="18" t="n"/>
+      <c r="T29" s="18" t="n"/>
+      <c r="U29" s="18" t="n"/>
+      <c r="V29" s="18" t="n"/>
+      <c r="W29" s="18" t="n"/>
+      <c r="X29" s="18" t="n"/>
+      <c r="Y29" s="18" t="n"/>
+      <c r="Z29" s="18" t="n"/>
+      <c r="AA29" s="18" t="n"/>
+      <c r="AB29" s="18" t="n"/>
+      <c r="AC29" s="18" t="n"/>
+      <c r="AD29" s="18" t="n"/>
+      <c r="AE29" s="18" t="n"/>
+    </row>
+    <row r="30" hidden="1">
+      <c r="A30" s="18" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="18" t="n"/>
+      <c r="M30" s="18" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="18" t="n"/>
+      <c r="P30" s="18" t="n"/>
+      <c r="Q30" s="18" t="n"/>
+      <c r="R30" s="18" t="n"/>
+      <c r="S30" s="18" t="n"/>
+      <c r="T30" s="18" t="n"/>
+      <c r="U30" s="18" t="n"/>
+      <c r="V30" s="18" t="n"/>
+      <c r="W30" s="18" t="n"/>
+      <c r="X30" s="18" t="n"/>
+      <c r="Y30" s="18" t="n"/>
+      <c r="Z30" s="18" t="n"/>
+      <c r="AA30" s="18" t="n"/>
+      <c r="AB30" s="18" t="n"/>
+      <c r="AC30" s="18" t="n"/>
+      <c r="AD30" s="18" t="n"/>
+      <c r="AE30" s="18" t="n"/>
+    </row>
+    <row r="31" hidden="1">
+      <c r="A31" s="18" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="18" t="n"/>
+      <c r="P31" s="18" t="n"/>
+      <c r="Q31" s="18" t="n"/>
+      <c r="R31" s="18" t="n"/>
+      <c r="S31" s="18" t="n"/>
+      <c r="T31" s="18" t="n"/>
+      <c r="U31" s="18" t="n"/>
+      <c r="V31" s="18" t="n"/>
+      <c r="W31" s="18" t="n"/>
+      <c r="X31" s="18" t="n"/>
+      <c r="Y31" s="18" t="n"/>
+      <c r="Z31" s="18" t="n"/>
+      <c r="AA31" s="18" t="n"/>
+      <c r="AB31" s="18" t="n"/>
+      <c r="AC31" s="18" t="n"/>
+      <c r="AD31" s="18" t="n"/>
+      <c r="AE31" s="18" t="n"/>
+    </row>
+    <row r="32" hidden="1">
+      <c r="A32" s="18" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="n"/>
+      <c r="L32" s="18" t="n"/>
+      <c r="M32" s="18" t="n"/>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="18" t="n"/>
+      <c r="P32" s="18" t="n"/>
+      <c r="Q32" s="18" t="n"/>
+      <c r="R32" s="18" t="n"/>
+      <c r="S32" s="18" t="n"/>
+      <c r="T32" s="18" t="n"/>
+      <c r="U32" s="18" t="n"/>
+      <c r="V32" s="18" t="n"/>
+      <c r="W32" s="18" t="n"/>
+      <c r="X32" s="18" t="n"/>
+      <c r="Y32" s="18" t="n"/>
+      <c r="Z32" s="18" t="n"/>
+      <c r="AA32" s="18" t="n"/>
+      <c r="AB32" s="18" t="n"/>
+      <c r="AC32" s="18" t="n"/>
+      <c r="AD32" s="18" t="n"/>
+      <c r="AE32" s="18" t="n"/>
+    </row>
+    <row r="33" hidden="1">
+      <c r="A33" s="18" t="n"/>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="18" t="n"/>
+      <c r="P33" s="18" t="n"/>
+      <c r="Q33" s="18" t="n"/>
+      <c r="R33" s="18" t="n"/>
+      <c r="S33" s="18" t="n"/>
+      <c r="T33" s="18" t="n"/>
+      <c r="U33" s="18" t="n"/>
+      <c r="V33" s="18" t="n"/>
+      <c r="W33" s="18" t="n"/>
+      <c r="X33" s="18" t="n"/>
+      <c r="Y33" s="18" t="n"/>
+      <c r="Z33" s="18" t="n"/>
+      <c r="AA33" s="18" t="n"/>
+      <c r="AB33" s="18" t="n"/>
+      <c r="AC33" s="18" t="n"/>
+      <c r="AD33" s="18" t="n"/>
+      <c r="AE33" s="18" t="n"/>
+    </row>
+    <row r="34" hidden="1">
+      <c r="A34" s="18" t="n"/>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="18" t="n"/>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="18" t="n"/>
+      <c r="M34" s="18" t="n"/>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="18" t="n"/>
+      <c r="P34" s="18" t="n"/>
+      <c r="Q34" s="18" t="n"/>
+      <c r="R34" s="18" t="n"/>
+      <c r="S34" s="18" t="n"/>
+      <c r="T34" s="18" t="n"/>
+      <c r="U34" s="18" t="n"/>
+      <c r="V34" s="18" t="n"/>
+      <c r="W34" s="18" t="n"/>
+      <c r="X34" s="18" t="n"/>
+      <c r="Y34" s="18" t="n"/>
+      <c r="Z34" s="18" t="n"/>
+      <c r="AA34" s="18" t="n"/>
+      <c r="AB34" s="18" t="n"/>
+      <c r="AC34" s="18" t="n"/>
+      <c r="AD34" s="18" t="n"/>
+      <c r="AE34" s="18" t="n"/>
+    </row>
+    <row r="35" hidden="1">
+      <c r="A35" s="18" t="n"/>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="18" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="18" t="n"/>
+      <c r="R35" s="18" t="n"/>
+      <c r="S35" s="18" t="n"/>
+      <c r="T35" s="18" t="n"/>
+      <c r="U35" s="18" t="n"/>
+      <c r="V35" s="18" t="n"/>
+      <c r="W35" s="18" t="n"/>
+      <c r="X35" s="18" t="n"/>
+      <c r="Y35" s="18" t="n"/>
+      <c r="Z35" s="18" t="n"/>
+      <c r="AA35" s="18" t="n"/>
+      <c r="AB35" s="18" t="n"/>
+      <c r="AC35" s="18" t="n"/>
+      <c r="AD35" s="18" t="n"/>
+      <c r="AE35" s="18" t="n"/>
+    </row>
+    <row r="36" hidden="1">
+      <c r="A36" s="18" t="n"/>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="18" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="18" t="n"/>
+      <c r="M36" s="18" t="n"/>
+      <c r="N36" s="18" t="n"/>
+      <c r="O36" s="18" t="n"/>
+      <c r="P36" s="18" t="n"/>
+      <c r="Q36" s="18" t="n"/>
+      <c r="R36" s="18" t="n"/>
+      <c r="S36" s="18" t="n"/>
+      <c r="T36" s="18" t="n"/>
+      <c r="U36" s="18" t="n"/>
+      <c r="V36" s="18" t="n"/>
+      <c r="W36" s="18" t="n"/>
+      <c r="X36" s="18" t="n"/>
+      <c r="Y36" s="18" t="n"/>
+      <c r="Z36" s="18" t="n"/>
+      <c r="AA36" s="18" t="n"/>
+      <c r="AB36" s="18" t="n"/>
+      <c r="AC36" s="18" t="n"/>
+      <c r="AD36" s="18" t="n"/>
+      <c r="AE36" s="18" t="n"/>
+    </row>
+    <row r="37" hidden="1">
+      <c r="A37" s="18" t="n"/>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="18" t="n"/>
+      <c r="M37" s="18" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+      <c r="P37" s="18" t="n"/>
+      <c r="Q37" s="18" t="n"/>
+      <c r="R37" s="18" t="n"/>
+      <c r="S37" s="18" t="n"/>
+      <c r="T37" s="18" t="n"/>
+      <c r="U37" s="18" t="n"/>
+      <c r="V37" s="18" t="n"/>
+      <c r="W37" s="18" t="n"/>
+      <c r="X37" s="18" t="n"/>
+      <c r="Y37" s="18" t="n"/>
+      <c r="Z37" s="18" t="n"/>
+      <c r="AA37" s="18" t="n"/>
+      <c r="AB37" s="18" t="n"/>
+      <c r="AC37" s="18" t="n"/>
+      <c r="AD37" s="18" t="n"/>
+      <c r="AE37" s="18" t="n"/>
+    </row>
+    <row r="38" hidden="1">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="18" t="n"/>
+      <c r="M38" s="18" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
+      <c r="P38" s="18" t="n"/>
+      <c r="Q38" s="18" t="n"/>
+      <c r="R38" s="18" t="n"/>
+      <c r="S38" s="18" t="n"/>
+      <c r="T38" s="18" t="n"/>
+      <c r="U38" s="18" t="n"/>
+      <c r="V38" s="18" t="n"/>
+      <c r="W38" s="18" t="n"/>
+      <c r="X38" s="18" t="n"/>
+      <c r="Y38" s="18" t="n"/>
+      <c r="Z38" s="18" t="n"/>
+      <c r="AA38" s="18" t="n"/>
+      <c r="AB38" s="18" t="n"/>
+      <c r="AC38" s="18" t="n"/>
+      <c r="AD38" s="18" t="n"/>
+      <c r="AE38" s="18" t="n"/>
+    </row>
+    <row r="39" hidden="1">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="n"/>
+      <c r="L39" s="18" t="n"/>
+      <c r="M39" s="18" t="n"/>
+      <c r="N39" s="18" t="n"/>
+      <c r="O39" s="18" t="n"/>
+      <c r="P39" s="18" t="n"/>
+      <c r="Q39" s="18" t="n"/>
+      <c r="R39" s="18" t="n"/>
+      <c r="S39" s="18" t="n"/>
+      <c r="T39" s="18" t="n"/>
+      <c r="U39" s="18" t="n"/>
+      <c r="V39" s="18" t="n"/>
+      <c r="W39" s="18" t="n"/>
+      <c r="X39" s="18" t="n"/>
+      <c r="Y39" s="18" t="n"/>
+      <c r="Z39" s="18" t="n"/>
+      <c r="AA39" s="18" t="n"/>
+      <c r="AB39" s="18" t="n"/>
+      <c r="AC39" s="18" t="n"/>
+      <c r="AD39" s="18" t="n"/>
+      <c r="AE39" s="18" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="B40" s="14" t="n"/>
@@ -2655,10 +2705,9 @@
       <c r="AE41" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="25">
     <mergeCell ref="B18:AE18"/>
     <mergeCell ref="B12:AE12"/>
-    <mergeCell ref="B21:AE21"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="Z3:AE3"/>
@@ -3842,8 +3891,8 @@
     <mergeCell ref="I26:N26"/>
     <mergeCell ref="Z26:AB26"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="W30:Y30"/>
     <mergeCell ref="D29:H29"/>
-    <mergeCell ref="W30:Y30"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="I16:N16"/>
@@ -3859,7 +3908,6 @@
     <mergeCell ref="I18:N18"/>
     <mergeCell ref="W22:Y22"/>
     <mergeCell ref="R26:T26"/>
-    <mergeCell ref="R29:T29"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="AC20:AE20"/>
@@ -3899,13 +3947,13 @@
     <mergeCell ref="U24:V24"/>
     <mergeCell ref="I31:N31"/>
     <mergeCell ref="U18:V18"/>
-    <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="Z30:AB30"/>
     <mergeCell ref="I6:N6"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="I15:N15"/>
     <mergeCell ref="D12:H12"/>
+    <mergeCell ref="R29:T29"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="W10:Y10"/>
     <mergeCell ref="R11:T11"/>
@@ -3939,10 +3987,10 @@
     <mergeCell ref="AC19:AE19"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="O27:Q27"/>
     <mergeCell ref="D26:H26"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="AC9:AE9"/>
     <mergeCell ref="I17:N17"/>
     <mergeCell ref="O17:Q17"/>
@@ -3970,6 +4018,7 @@
     <mergeCell ref="I30:N30"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="W6:Y6"/>
+    <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="I11:N11"/>
     <mergeCell ref="O6:Q6"/>
